--- a/leads_with_explanations_v0.xlsx
+++ b/leads_with_explanations_v0.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DN3"/>
+  <dimension ref="A1:DP3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -563,6 +563,8 @@
     <col width="80" customWidth="1" min="116" max="116"/>
     <col width="60" customWidth="1" min="117" max="117"/>
     <col width="18" customWidth="1" min="118" max="118"/>
+    <col width="18" customWidth="1" min="119" max="119"/>
+    <col width="18" customWidth="1" min="120" max="120"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1156,6 +1158,16 @@
           <t>llm_duration_sec</t>
         </is>
       </c>
+      <c r="DO1" s="2" t="inlineStr">
+        <is>
+          <t>llm_confidence_pct</t>
+        </is>
+      </c>
+      <c r="DP1" s="2" t="inlineStr">
+        <is>
+          <t>llm_confidence_reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1603,14 +1615,24 @@
       </c>
       <c r="DL2" s="3" t="inlineStr">
         <is>
-          <t>Here is the narrative paragraph:
-Meet LD-100015, a converted lead from Avflight Corporation, a commercial aviation partner in Western Europe. This COLD-rated lead has a predicted conversion probability of 4.6%, indicating a decent chance of closing. What's working in our favor is strong engagement on our website, with high scores for time on site and purchase history. Additionally, the lead's email opens suggest they're interested in learning more about our safety systems. However, there are some concerns - the lead's loyalty score is low, indicating a higher likelihood of being influenced by competitors. Furthermore, the referral source and location score may also pose challenges. To move forward, I recommend that you prioritize building on the positive signals, such as following up with a personalized email campaign to further educate Avflight Corporation about our safety systems, while also addressing the negative signals head-on.</t>
+          <t>This lead shows strong potential for conversion due to high engagement activity, clear product interest, and a verified corporate account. The opportunity is supported by strong commercial intent signals and healthy demographic alignment, suggesting the prospect is actively evaluating solutions. While some negative signals exist, such as limited phone availability, they do not significantly impact the overall conversion likelihood. A personalized outreach focused on product fit and timing would likely improve conversion chances.</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>Based on the following lead data, write a storytelling paragraph that explains this lead 
-to a sales representative in a natural, insightful, and action-oriented way.
+          <t>Example 1:
+{
+  "lead_story": "This lead shows strong conversion potential due to high engagement activity, clear product interest, and a verified corporate account. The opportunity is supported by strong commercial intent signals and healthy demographic alignment, suggesting the prospect is actively evaluating solutions. However, limited phone availability and incomplete lead descriptions may slow direct outreach effectiveness. The lead is currently rated as high quality with a strong predicted conversion likelihood, making it suitable for immediate follow-up by the regional sales team. A personalized outreach focused on product fit and timing would likely improve conversion chances.",
+  "confidence_pct": 91,
+  "confidence_reason": "High confidence due to strong engagement signals, verified corporate data, multiple aligned intent indicators, and minimal missing information."
+}
+Example 2:
+{
+  "lead_story": "This lead demonstrates moderate sales potential but contains several data gaps that reduce certainty around purchase intent. While the account appears to have some engagement activity and aligns with early intent indicators, weak contact coverage and limited supporting behavioral evidence create uncertainty around readiness to convert. The predicted conversion likelihood remains moderate, though negative conversion drivers suggest the lead may still be in an exploratory phase. Sales outreach should focus on validating current business needs and confirming decision-maker engagement before prioritizing further resources.",
+  "confidence_pct": 63,
+  "confidence_reason": "Moderate confidence because several important engagement and contact signals are missing or weak."
+}
+Now generate the JSON output for this lead.
 LEAD SUMMARY
 ------------
 Lead ID       : LD-100015
@@ -1635,30 +1657,39 @@
 Behavior Score                   : 34.8/100
 Demographic Score                : 51.4/100
 Engagement Score                 : 70.5/100
-Confidence                       : 90.7%
-KEY CONVERSION DRIVERS (from SHAP analysis)
---------------------------------------------
+Model Confidence                 : 90.7%
+KEY CONVERSION DRIVERS
+----------------------
 Positive Signals:
-  (+) Ad Impressions: strongly supports conversion
-  (+) Time on Site: strongly supports conversion
-  (+) Purchase History: strongly supports conversion
-  (+) Engagement Rate: strongly supports conversion
-  (+) Email Opens: strongly supports conversion
+(+) Ad Impressions
+(+) Time on Site
+(+) Purchase History
+(+) Engagement Rate
+(+) Email Opens
 Negative Signals:
-  (-) Trial Conversions: acts as a barrier to conversion
-  (-) Referral Source: acts as a barrier to conversion
-  (-) Location Score: acts as a barrier to conversion
-  (-) Device Type: acts as a barrier to conversion
-  (-) Plan Type: acts as a barrier to conversion
+(-) Trial Conversions
+(-) Referral Source
+(-) Location Score
+(-) Device Type
+(-) Plan Type
 TOPIC ALIGNMENT SIGNALS
 -----------------------
-Aligned    : Lead Description Completeness, Lead Score &amp; Stage, Corporate Email Address, Source Awareness, Strong Commercial Intent, FSE Generated Lead
-Not Aligned: Existing Customer Validity, Early Intent Signal
-Your narrative paragraph:</t>
+Aligned:
+Lead Description Completeness, Lead Score &amp; Stage, Corporate Email Address, Source Awareness, Strong Commercial Intent, FSE Generated Lead
+Not Aligned:
+Existing Customer Validity, Early Intent Signal</t>
         </is>
       </c>
       <c r="DN2" t="n">
-        <v>104.58</v>
+        <v>75.72</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>85</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>High confidence due to strong engagement signals, verified corporate data, multiple aligned intent indicators, and minimal missing information, despite some negative signals.</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2107,14 +2138,24 @@
       </c>
       <c r="DL3" s="3" t="inlineStr">
         <is>
-          <t>Here's a storytelling paragraph that explains this lead to a sales representative:
-You've got a great opportunity with Wheels Up Partners, a competitor in the MRO market. Although they're not an existing customer, their medium loyalty score suggests there may be potential for future business. The fact that they're interested in upgrading their Bombardier Global 7500's avionics is a strong positive signal, as is their relatively high engagement score. However, we do see some red flags - specifically, the lack of demo requests and email opens, which could indicate a need to build more trust before moving forward. Our model suggests this lead has a moderate conversion probability (26.9%), but it's not entirely out of reach. To capitalize on this opportunity, I recommend reaching out via their corporate email address and exploring their needs in more detail.</t>
+          <t>This lead presents a moderate sales opportunity with some positive conversion drivers. The presence of cart abandonment and trial conversions suggests the prospect has shown interest in purchasing avionics upgrades for their Bombardier Global 7500 aircraft. However, limited engagement signals and conflicting negative indicators, such as demo requests and low location score, create uncertainty around purchase intent. A personalized outreach focused on validating current business needs and confirming decision-maker engagement would be necessary to prioritize further resources. Despite some data gaps, the lead's medium loyalty level and strong commercial intent suggest it may still be worth pursuing.</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>Based on the following lead data, write a storytelling paragraph that explains this lead 
-to a sales representative in a natural, insightful, and action-oriented way.
+          <t>Example 1:
+{
+  "lead_story": "This lead shows strong conversion potential due to high engagement activity, clear product interest, and a verified corporate account. The opportunity is supported by strong commercial intent signals and healthy demographic alignment, suggesting the prospect is actively evaluating solutions. However, limited phone availability and incomplete lead descriptions may slow direct outreach effectiveness. The lead is currently rated as high quality with a strong predicted conversion likelihood, making it suitable for immediate follow-up by the regional sales team. A personalized outreach focused on product fit and timing would likely improve conversion chances.",
+  "confidence_pct": 91,
+  "confidence_reason": "High confidence due to strong engagement signals, verified corporate data, multiple aligned intent indicators, and minimal missing information."
+}
+Example 2:
+{
+  "lead_story": "This lead demonstrates moderate sales potential but contains several data gaps that reduce certainty around purchase intent. While the account appears to have some engagement activity and aligns with early intent indicators, weak contact coverage and limited supporting behavioral evidence create uncertainty around readiness to convert. The predicted conversion likelihood remains moderate, though negative conversion drivers suggest the lead may still be in an exploratory phase. Sales outreach should focus on validating current business needs and confirming decision-maker engagement before prioritizing further resources.",
+  "confidence_pct": 63,
+  "confidence_reason": "Moderate confidence because several important engagement and contact signals are missing or weak."
+}
+Now generate the JSON output for this lead.
 LEAD SUMMARY
 ------------
 Lead ID       : LD-100017
@@ -2139,30 +2180,39 @@
 Behavior Score                   : 89.1/100
 Demographic Score                : 59.4/100
 Engagement Score                 : 61.1/100
-Confidence                       : 46.2%
-KEY CONVERSION DRIVERS (from SHAP analysis)
---------------------------------------------
+Model Confidence                 : 46.2%
+KEY CONVERSION DRIVERS
+----------------------
 Positive Signals:
-  (+) Cart Abandonment: strongly supports conversion
-  (+) Trial Conversions: strongly supports conversion
-  (+) Revenue Potential: strongly supports conversion
-  (+) Lead Behavior: strongly supports conversion
-  (+) Purchase History: strongly supports conversion
+(+) Cart Abandonment
+(+) Trial Conversions
+(+) Revenue Potential
+(+) Lead Behavior
+(+) Purchase History
 Negative Signals:
-  (-) Demo Requests: acts as a barrier to conversion
-  (-) Email Opens: acts as a barrier to conversion
-  (-) Location Score: acts as a barrier to conversion
-  (-) API Calls: acts as a barrier to conversion
-  (-) Session Duration: acts as a barrier to conversion
+(-) Demo Requests
+(-) Email Opens
+(-) Location Score
+(-) API Calls
+(-) Session Duration
 TOPIC ALIGNMENT SIGNALS
 -----------------------
-Aligned    : Corporate Email Address, Existing Customer Validity, Source Awareness, Early Intent Signal, Strong Commercial Intent
-Not Aligned: Lead Description Completeness, Lead Score &amp; Stage, FSE Generated Lead
-Your narrative paragraph:</t>
+Aligned:
+Corporate Email Address, Existing Customer Validity, Source Awareness, Early Intent Signal, Strong Commercial Intent
+Not Aligned:
+Lead Description Completeness, Lead Score &amp; Stage, FSE Generated Lead</t>
         </is>
       </c>
       <c r="DN3" t="n">
-        <v>92.17</v>
+        <v>82.06999999999999</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>72</v>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>Moderate confidence due to mixed positive and negative signals, incomplete lead descriptions, and limited engagement evidence.</t>
+        </is>
       </c>
     </row>
   </sheetData>
